--- a/output/pdf_financials_xlsx/DLP.xlsx
+++ b/output/pdf_financials_xlsx/DLP.xlsx
@@ -931,13 +931,13 @@
         <v>-0.000145</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.262756</v>
+        <v>-1.262756</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.262756</v>
+        <v>-1.262756</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.480178</v>
+        <v>-2.480178</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>1.85161</v>
@@ -974,16 +974,16 @@
         <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-3.70322</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-7.628864</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-14.187096</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-14.298946</v>
       </c>
     </row>
     <row r="18">
@@ -1103,25 +1103,25 @@
         <v>-0.000145</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.262756</v>
+        <v>-1.262756</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.262756</v>
+        <v>-1.262756</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.480178</v>
+        <v>-2.480178</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.85161</v>
+        <v>-1.85161</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.814432</v>
+        <v>-3.814432</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>7.093548</v>
+        <v>-7.093548</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>7.149473</v>
+        <v>-7.149473</v>
       </c>
     </row>
     <row r="21">
@@ -1205,25 +1205,25 @@
         <v>-0.000145</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.262756</v>
+        <v>-1.262756</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.262756</v>
+        <v>-1.262756</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.480178</v>
+        <v>-2.480178</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.85161</v>
+        <v>-1.85161</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>3.814432</v>
+        <v>-3.814432</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>7.093548</v>
+        <v>-7.093548</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>7.149473</v>
+        <v>-7.149473</v>
       </c>
     </row>
     <row r="24">
@@ -1327,19 +1327,19 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>62.00445</v>
+        <v>-62.00445</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>61.720333</v>
+        <v>-61.720333</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>76.28864</v>
+        <v>-76.28864</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>101.3364</v>
+        <v>-101.3364</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>119.157883</v>
+        <v>-119.157883</v>
       </c>
     </row>
     <row r="27">
@@ -1355,13 +1355,13 @@
         <v>-0.000145</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.262756</v>
+        <v>-1.262756</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.262756</v>
+        <v>-1.262756</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.480178</v>
+        <v>-2.480178</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>1.85161</v>
@@ -1423,13 +1423,13 @@
         <v>-0.000145</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.262756</v>
+        <v>-1.262756</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.262756</v>
+        <v>-1.262756</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.480178</v>
+        <v>-2.480178</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>1.85161</v>
@@ -1509,25 +1509,25 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32">
@@ -3751,22 +3751,22 @@
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.188314</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.317294</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.7904640000000001</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.872802</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.321391</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>7.162096</v>
       </c>
     </row>
     <row r="93">
@@ -6187,7 +6187,11 @@
           <t>Share-based payment reserves 9</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -7066,7 +7070,11 @@
           <t>Share-based payment reserves 8</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -7312,7 +7320,11 @@
           <t>Share‐based payment reserves 8</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -7869,7 +7881,11 @@
           <t>Share‐based payment reserves 10</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -16548,10 +16564,10 @@
         </is>
       </c>
       <c r="L188" s="5" t="n">
-        <v>7.093548</v>
+        <v>-7.093548</v>
       </c>
       <c r="M188" s="5" t="n">
-        <v>7.149473</v>
+        <v>-7.149473</v>
       </c>
     </row>
     <row r="189">
@@ -17199,13 +17215,13 @@
         </is>
       </c>
       <c r="J199" s="5" t="n">
-        <v>1.85161</v>
+        <v>-1.85161</v>
       </c>
       <c r="K199" s="5" t="n">
-        <v>3.814432</v>
+        <v>-3.814432</v>
       </c>
       <c r="L199" s="5" t="n">
-        <v>7.093548</v>
+        <v>-7.093548</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
@@ -17900,10 +17916,10 @@
         </is>
       </c>
       <c r="I211" s="5" t="n">
-        <v>2.480178</v>
+        <v>-2.480178</v>
       </c>
       <c r="J211" s="5" t="n">
-        <v>1.85161</v>
+        <v>-1.85161</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
@@ -18694,10 +18710,10 @@
         </is>
       </c>
       <c r="H224" s="5" t="n">
-        <v>1.262756</v>
+        <v>-1.262756</v>
       </c>
       <c r="I224" s="5" t="n">
-        <v>2.480178</v>
+        <v>-2.480178</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -19301,7 +19317,7 @@
         </is>
       </c>
       <c r="G234" s="5" t="n">
-        <v>1.262756</v>
+        <v>-1.262756</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/DLP.xlsx
+++ b/output/pdf_financials_xlsx/DLP.xlsx
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>2.4e-05</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000685</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.066715</v>
       </c>
     </row>
     <row r="13">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.000145</v>
+        <v>-0.000169</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.000145</v>
+        <v>-0.00083</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.262756</v>
@@ -1373,7 +1373,7 @@
         <v>7.093548</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>7.149473</v>
+        <v>7.216188</v>
       </c>
     </row>
     <row r="28">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.000145</v>
+        <v>-0.000169</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.000145</v>
+        <v>-0.00083</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.262756</v>
@@ -1441,7 +1441,7 @@
         <v>7.093548</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>7.149473</v>
+        <v>7.216188</v>
       </c>
     </row>
     <row r="30">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.145097</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.256175</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -1607,22 +1607,22 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.414728</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.154193</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.207697</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.964346</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.286839</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.82063</v>
       </c>
     </row>
     <row r="35">
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.145097</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.256175</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -1679,22 +1679,22 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.414728</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.154193</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.207697</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.964346</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.286839</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.82063</v>
       </c>
     </row>
     <row r="37">
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.150097</v>
+        <v>0.005</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.256175</v>
+        <v>0</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
@@ -2111,22 +2111,22 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.432782</v>
+        <v>0.018054</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.233643</v>
+        <v>0.07945000000000001</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.361428</v>
+        <v>0.153731</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.973488</v>
+        <v>0.009142000000000001</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.363588</v>
+        <v>0.076749</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.830191</v>
+        <v>0.009561</v>
       </c>
     </row>
     <row r="49">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5780,7 +5780,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -6836,7 +6840,11 @@
           <t>Reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -7633,7 +7641,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -8190,7 +8202,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -8253,7 +8269,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
@@ -10521,7 +10537,11 @@
           <t>Increase in reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -11304,7 +11324,11 @@
           <t>Increase in reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -13153,7 +13177,11 @@
           <t>Increase in reclamation deposit</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -13995,7 +14023,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -16338,7 +16370,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -19368,7 +19400,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E235" s="5" t="n">

--- a/output/pdf_financials_xlsx/DLP.xlsx
+++ b/output/pdf_financials_xlsx/DLP.xlsx
@@ -9709,7 +9709,11 @@
           <t>Proceeds from share issuances 8</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -11444,7 +11448,11 @@
           <t>Proceeds from share issuances 7</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -13299,7 +13307,11 @@
           <t>Proceeds from share issuance 9</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -14271,7 +14283,11 @@
           <t>Proceeds from share issuance 7</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
